--- a/Projects/Datasets for Excel/Datasets for excel/highlight_cells.xlsx
+++ b/Projects/Datasets for Excel/Datasets for excel/highlight_cells.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shahriar/Desktop/PROJECTs/Course/Data - Excel/8. highlight cells/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DS\tezendra\Projects\Datasets for Excel\Datasets for excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B26AA5C-3B21-EE47-8B50-588AD121372F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3A18C3A-0B68-4A73-9DEF-EAE36D20054D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$201</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
@@ -115,7 +118,26 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -415,15 +437,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:D201"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="12.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="12.125" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -437,7 +460,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -451,7 +474,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -465,7 +488,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -479,7 +502,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -493,7 +516,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -507,7 +530,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -521,7 +544,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -535,7 +558,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -549,7 +572,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -563,7 +586,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -577,7 +600,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -591,7 +614,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -605,7 +628,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -619,7 +642,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -633,7 +656,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -647,7 +670,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -661,7 +684,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -675,7 +698,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -689,7 +712,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -703,7 +726,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -717,7 +740,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -731,7 +754,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -745,7 +768,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -759,7 +782,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -773,7 +796,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -787,7 +810,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -801,7 +824,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -815,7 +838,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -829,7 +852,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -843,7 +866,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -857,7 +880,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -871,7 +894,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -885,7 +908,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -899,7 +922,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -913,7 +936,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -927,7 +950,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -941,7 +964,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -955,7 +978,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -969,7 +992,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -983,7 +1006,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -997,7 +1020,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1011,7 +1034,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1025,7 +1048,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1039,7 +1062,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -1053,7 +1076,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -1067,7 +1090,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -1081,7 +1104,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1095,7 +1118,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1109,7 +1132,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1123,7 +1146,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1137,7 +1160,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -1151,7 +1174,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -1165,7 +1188,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -1179,7 +1202,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -1193,7 +1216,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -1207,7 +1230,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -1221,7 +1244,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -1235,7 +1258,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -1249,7 +1272,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -1263,7 +1286,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -1277,7 +1300,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -1291,7 +1314,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -1305,7 +1328,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -1319,7 +1342,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -1333,7 +1356,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
@@ -1347,7 +1370,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
@@ -1361,7 +1384,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -1375,7 +1398,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
@@ -1389,7 +1412,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
@@ -1403,7 +1426,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
@@ -1417,7 +1440,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
@@ -1431,7 +1454,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
@@ -1445,7 +1468,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
@@ -1459,7 +1482,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
@@ -1473,7 +1496,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
@@ -1487,7 +1510,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
@@ -1501,7 +1524,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
@@ -1515,7 +1538,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
@@ -1529,7 +1552,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
@@ -1543,7 +1566,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
@@ -1557,7 +1580,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
@@ -1571,7 +1594,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
@@ -1585,7 +1608,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
@@ -1599,7 +1622,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
@@ -1613,7 +1636,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
@@ -1627,7 +1650,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
@@ -1641,7 +1664,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
@@ -1655,7 +1678,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
@@ -1669,7 +1692,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
@@ -1683,7 +1706,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
@@ -1697,7 +1720,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
@@ -1711,7 +1734,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
@@ -1725,7 +1748,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
@@ -1739,7 +1762,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
@@ -1753,7 +1776,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
@@ -1767,7 +1790,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
@@ -1781,7 +1804,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
@@ -1795,7 +1818,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
@@ -1809,7 +1832,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
@@ -1823,7 +1846,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
@@ -1837,7 +1860,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>101</v>
       </c>
@@ -1851,7 +1874,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>102</v>
       </c>
@@ -1865,7 +1888,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>103</v>
       </c>
@@ -1879,7 +1902,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>104</v>
       </c>
@@ -1893,7 +1916,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>105</v>
       </c>
@@ -1907,7 +1930,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>106</v>
       </c>
@@ -1921,7 +1944,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>107</v>
       </c>
@@ -1935,7 +1958,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>108</v>
       </c>
@@ -1949,7 +1972,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>109</v>
       </c>
@@ -1963,7 +1986,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>110</v>
       </c>
@@ -1977,7 +2000,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>111</v>
       </c>
@@ -1991,7 +2014,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>112</v>
       </c>
@@ -2005,7 +2028,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>113</v>
       </c>
@@ -2019,7 +2042,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>114</v>
       </c>
@@ -2033,7 +2056,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>115</v>
       </c>
@@ -2047,7 +2070,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>116</v>
       </c>
@@ -2061,7 +2084,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>117</v>
       </c>
@@ -2075,7 +2098,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>118</v>
       </c>
@@ -2089,7 +2112,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>119</v>
       </c>
@@ -2103,7 +2126,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>120</v>
       </c>
@@ -2117,7 +2140,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>121</v>
       </c>
@@ -2131,7 +2154,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>122</v>
       </c>
@@ -2145,7 +2168,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>123</v>
       </c>
@@ -2159,7 +2182,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>124</v>
       </c>
@@ -2173,7 +2196,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>125</v>
       </c>
@@ -2187,7 +2210,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>126</v>
       </c>
@@ -2201,7 +2224,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>127</v>
       </c>
@@ -2215,7 +2238,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>128</v>
       </c>
@@ -2229,7 +2252,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>129</v>
       </c>
@@ -2243,7 +2266,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>130</v>
       </c>
@@ -2257,7 +2280,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>131</v>
       </c>
@@ -2271,7 +2294,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>132</v>
       </c>
@@ -2285,7 +2308,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>133</v>
       </c>
@@ -2299,7 +2322,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>134</v>
       </c>
@@ -2313,7 +2336,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>135</v>
       </c>
@@ -2327,7 +2350,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>136</v>
       </c>
@@ -2341,7 +2364,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>137</v>
       </c>
@@ -2355,7 +2378,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>138</v>
       </c>
@@ -2369,7 +2392,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>139</v>
       </c>
@@ -2383,7 +2406,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>140</v>
       </c>
@@ -2397,7 +2420,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>141</v>
       </c>
@@ -2411,7 +2434,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>142</v>
       </c>
@@ -2425,7 +2448,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>143</v>
       </c>
@@ -2439,7 +2462,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>144</v>
       </c>
@@ -2453,7 +2476,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>145</v>
       </c>
@@ -2467,7 +2490,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>146</v>
       </c>
@@ -2481,7 +2504,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>147</v>
       </c>
@@ -2495,7 +2518,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>148</v>
       </c>
@@ -2509,7 +2532,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>149</v>
       </c>
@@ -2523,7 +2546,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>150</v>
       </c>
@@ -2537,7 +2560,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>151</v>
       </c>
@@ -2551,7 +2574,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>152</v>
       </c>
@@ -2565,7 +2588,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>153</v>
       </c>
@@ -2579,7 +2602,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>154</v>
       </c>
@@ -2593,7 +2616,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>155</v>
       </c>
@@ -2607,7 +2630,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>156</v>
       </c>
@@ -2621,7 +2644,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>157</v>
       </c>
@@ -2635,7 +2658,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>158</v>
       </c>
@@ -2649,7 +2672,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>159</v>
       </c>
@@ -2663,7 +2686,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>160</v>
       </c>
@@ -2677,7 +2700,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>161</v>
       </c>
@@ -2691,7 +2714,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>162</v>
       </c>
@@ -2705,7 +2728,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>163</v>
       </c>
@@ -2719,7 +2742,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>164</v>
       </c>
@@ -2733,7 +2756,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>165</v>
       </c>
@@ -2747,7 +2770,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>166</v>
       </c>
@@ -2761,7 +2784,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>167</v>
       </c>
@@ -2775,7 +2798,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>168</v>
       </c>
@@ -2789,7 +2812,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>169</v>
       </c>
@@ -2803,7 +2826,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>170</v>
       </c>
@@ -2817,7 +2840,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>171</v>
       </c>
@@ -2831,7 +2854,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>172</v>
       </c>
@@ -2845,7 +2868,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>173</v>
       </c>
@@ -2859,7 +2882,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>174</v>
       </c>
@@ -2873,7 +2896,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>175</v>
       </c>
@@ -2887,7 +2910,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>176</v>
       </c>
@@ -2901,7 +2924,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>177</v>
       </c>
@@ -2915,7 +2938,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>178</v>
       </c>
@@ -2929,7 +2952,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>179</v>
       </c>
@@ -2943,7 +2966,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>180</v>
       </c>
@@ -2957,7 +2980,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>181</v>
       </c>
@@ -2971,7 +2994,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>182</v>
       </c>
@@ -2985,7 +3008,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>183</v>
       </c>
@@ -2999,7 +3022,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>184</v>
       </c>
@@ -3013,7 +3036,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>185</v>
       </c>
@@ -3027,7 +3050,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>186</v>
       </c>
@@ -3041,7 +3064,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>187</v>
       </c>
@@ -3055,7 +3078,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>188</v>
       </c>
@@ -3069,7 +3092,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>189</v>
       </c>
@@ -3083,7 +3106,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>190</v>
       </c>
@@ -3097,7 +3120,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>191</v>
       </c>
@@ -3111,7 +3134,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>192</v>
       </c>
@@ -3125,7 +3148,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>193</v>
       </c>
@@ -3139,7 +3162,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>194</v>
       </c>
@@ -3153,7 +3176,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>195</v>
       </c>
@@ -3167,7 +3190,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>196</v>
       </c>
@@ -3181,7 +3204,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>197</v>
       </c>
@@ -3195,7 +3218,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>198</v>
       </c>
@@ -3209,7 +3232,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>199</v>
       </c>
@@ -3223,7 +3246,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>200</v>
       </c>
@@ -3238,6 +3261,21 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D201" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="2">
+      <customFilters>
+        <customFilter operator="lessThanOrEqual" val="500"/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="3">
+      <colorFilter dxfId="0"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="D1:D1048576">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Toys &amp; Games">
+      <formula>NOT(ISERROR(SEARCH("Toys &amp; Games",D1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>